--- a/branches/fix/footer-publisher/all-profiles.xlsx
+++ b/branches/fix/footer-publisher/all-profiles.xlsx
@@ -66,7 +66,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-30T15:49:56+00:00</t>
+    <t>2026-07-30T16:02:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
